--- a/Undigitized_Records_2026_03_13.xlsx
+++ b/Undigitized_Records_2026_03_13.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sotonac-my.sharepoint.com/personal/ck1g20_soton_ac_uk/Documents/Documents/PhD/20_Historical_record_catalogue/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="8_{2EBFFBB5-AA1D-4DD9-A43A-243907206CD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA95233B-F5C4-490A-9185-415B6D756802}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="8_{2EBFFBB5-AA1D-4DD9-A43A-243907206CD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69D2F30A-5876-4C50-A01C-8357B9988424}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B145EA35-1BD5-495C-A7E0-BAB6ECA9BC95}"/>
   </bookViews>
@@ -2782,6 +2782,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13522,7 +13526,7 @@
         <v>-20.297491000000001</v>
       </c>
       <c r="E261" s="12">
-        <v>-20.297491000000001</v>
+        <v>44.269697999999998</v>
       </c>
       <c r="F261" s="7">
         <v>1948</v>
